--- a/data/trans_dic/P0902-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P0902-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que dejó de hacer algunas tareas por problemas físicos</t>
+          <t>Población que dejó de hacer algunas tareas por problemas físicos (tasa de respuesta: 99,96%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>13,38; 17,78</t>
+          <t>13,46; 17,82</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>20,26; 26,02</t>
+          <t>20,61; 26,46</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17,62; 23,56</t>
+          <t>17,69; 23,55</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>24,17; 31,52</t>
+          <t>23,98; 31,34</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>21,17; 25,83</t>
+          <t>21,1; 25,93</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>32,97; 38,23</t>
+          <t>32,73; 38,3</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>31,79; 38,18</t>
+          <t>31,49; 38,17</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>39,3; 44,99</t>
+          <t>39,24; 45,19</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>18,2; 21,58</t>
+          <t>18,34; 21,74</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>28,34; 32,43</t>
+          <t>28,5; 32,4</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>26,53; 31,03</t>
+          <t>26,67; 30,96</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>34,13; 38,31</t>
+          <t>34,22; 38,46</t>
         </is>
       </c>
     </row>
@@ -857,52 +857,52 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,0; 6,27</t>
+          <t>4,0; 6,11</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,14; 7,36</t>
+          <t>5,22; 7,35</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,28; 7,37</t>
+          <t>5,22; 7,5</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,51; 11,36</t>
+          <t>6,95; 11,36</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,97; 10,75</t>
+          <t>7,84; 10,77</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,76; 12,96</t>
+          <t>9,83; 12,96</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,03; 13,07</t>
+          <t>10,08; 13,07</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>8,96; 14,48</t>
+          <t>9,36; 14,48</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,15; 7,94</t>
+          <t>6,13; 7,87</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7,72; 9,56</t>
+          <t>7,68; 9,47</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -912,7 +912,7 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,8; 12,37</t>
+          <t>8,94; 12,5</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,64; 6,17</t>
+          <t>2,61; 6,32</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,68; 8,56</t>
+          <t>3,81; 8,82</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,12; 7,24</t>
+          <t>3,11; 7,29</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,74; 10,12</t>
+          <t>5,85; 10,18</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,78; 11,37</t>
+          <t>5,93; 10,93</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,5; 10,78</t>
+          <t>5,43; 10,67</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,56; 12,03</t>
+          <t>6,52; 12,03</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,27; 11,03</t>
+          <t>7,41; 10,93</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,68; 7,78</t>
+          <t>4,59; 7,78</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5,09; 8,5</t>
+          <t>5,12; 8,87</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5,4; 9,09</t>
+          <t>5,4; 8,6</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,97; 9,68</t>
+          <t>7,15; 9,84</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,29; 9,22</t>
+          <t>7,28; 9,27</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,84; 12,05</t>
+          <t>10,01; 12,2</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,21; 10,25</t>
+          <t>8,27; 10,32</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9,35; 13,35</t>
+          <t>8,9; 13,31</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>13,37; 15,84</t>
+          <t>13,38; 15,79</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,66; 21,45</t>
+          <t>18,6; 21,39</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,36; 18,93</t>
+          <t>16,3; 19,14</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>14,67; 19,6</t>
+          <t>15,08; 19,84</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>10,73; 12,26</t>
+          <t>10,69; 12,26</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>14,66; 16,47</t>
+          <t>14,64; 16,41</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>12,7; 14,51</t>
+          <t>12,7; 14,4</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>13,09; 16,23</t>
+          <t>13,04; 16,19</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que dejó de hacer algunas tareas por problemas físicos</t>
+          <t>Población que dejó de hacer algunas tareas por problemas físicos (tasa de respuesta: 99,96%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>138077; 183486</t>
+          <t>138890; 183896</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>197472; 253554</t>
+          <t>200901; 257857</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>132917; 177720</t>
+          <t>133434; 177643</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>124295; 162087</t>
+          <t>123284; 161129</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>278407; 339721</t>
+          <t>277495; 341007</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>441104; 511466</t>
+          <t>437926; 512355</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>316197; 379727</t>
+          <t>313184; 379704</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>296885; 339894</t>
+          <t>296488; 341407</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>427221; 506420</t>
+          <t>430422; 510117</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>655354; 749858</t>
+          <t>658947; 749267</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>464007; 542660</t>
+          <t>466401; 541511</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>433325; 486414</t>
+          <t>434424; 488366</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>67663; 106166</t>
+          <t>67811; 103491</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>100919; 144555</t>
+          <t>102391; 144346</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>109616; 153058</t>
+          <t>108296; 155754</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>149039; 260020</t>
+          <t>159054; 260048</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>126502; 170682</t>
+          <t>124527; 170993</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>171303; 227496</t>
+          <t>172548; 227478</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>199416; 259917</t>
+          <t>200457; 259932</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>200401; 323877</t>
+          <t>209397; 323867</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>201686; 260657</t>
+          <t>201146; 258335</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>287060; 355425</t>
+          <t>285561; 352069</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>324056; 399212</t>
+          <t>323873; 399351</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>397992; 559725</t>
+          <t>404614; 565344</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>14577; 34032</t>
+          <t>14416; 34852</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>17722; 41171</t>
+          <t>18348; 42424</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>17075; 39614</t>
+          <t>17027; 39883</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>37129; 65437</t>
+          <t>37797; 65849</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>27520; 54165</t>
+          <t>28245; 52060</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>25191; 49319</t>
+          <t>24849; 48828</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>36034; 66048</t>
+          <t>35827; 66061</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>48033; 72845</t>
+          <t>48950; 72165</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>48139; 79982</t>
+          <t>47151; 79997</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>47770; 79818</t>
+          <t>48087; 83322</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>59189; 99618</t>
+          <t>59164; 94298</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>91081; 126563</t>
+          <t>93495; 128589</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>238988; 302230</t>
+          <t>238484; 303784</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>336437; 411889</t>
+          <t>342387; 417160</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>277369; 346241</t>
+          <t>279454; 348669</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>322593; 460278</t>
+          <t>307117; 458928</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>451936; 535285</t>
+          <t>452227; 533460</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>662424; 761585</t>
+          <t>660382; 759563</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>577812; 668724</t>
+          <t>575906; 676220</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>535610; 715984</t>
+          <t>550602; 724485</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>713886; 816233</t>
+          <t>711231; 815883</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1021915; 1147552</t>
+          <t>1020506; 1143885</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>877560; 1002585</t>
+          <t>877347; 994714</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>929642; 1152497</t>
+          <t>926296; 1149995</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P0902-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P0902-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>26,17%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>42,12%</t>
+          <t>41,62%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>36,18%</t>
+          <t>35,24%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>13,46; 17,82</t>
+          <t>13,41; 17,94</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>20,61; 26,46</t>
+          <t>20,44; 26,54</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17,69; 23,55</t>
+          <t>18,01; 23,4</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23,98; 31,34</t>
+          <t>22,94; 29,5</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>21,1; 25,93</t>
+          <t>21,2; 25,81</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>32,73; 38,3</t>
+          <t>32,89; 38,28</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>31,49; 38,17</t>
+          <t>31,66; 37,89</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>39,24; 45,19</t>
+          <t>38,99; 44,41</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>18,34; 21,74</t>
+          <t>18,46; 21,5</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>28,5; 32,4</t>
+          <t>28,3; 32,34</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>26,67; 30,96</t>
+          <t>26,39; 30,85</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>34,22; 38,46</t>
+          <t>33,44; 37,57</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>12,56%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,0; 6,11</t>
+          <t>4,02; 6,1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,22; 7,35</t>
+          <t>4,89; 7,3</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,22; 7,5</t>
+          <t>5,31; 7,5</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,95; 11,36</t>
+          <t>9,3; 11,96</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,84; 10,77</t>
+          <t>7,8; 10,71</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,83; 12,96</t>
+          <t>9,91; 13,05</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,08; 13,07</t>
+          <t>10,0; 13,06</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>9,36; 14,48</t>
+          <t>13,27; 15,92</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,13; 7,87</t>
+          <t>6,18; 7,91</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7,68; 9,47</t>
+          <t>7,7; 9,67</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7,97; 9,82</t>
+          <t>7,9; 9,73</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,94; 12,5</t>
+          <t>11,57; 13,55</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,62%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,61; 6,32</t>
+          <t>2,69; 6,35</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,81; 8,82</t>
+          <t>3,93; 8,87</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,11; 7,29</t>
+          <t>3,22; 7,33</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,85; 10,18</t>
+          <t>5,6; 9,67</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,93; 10,93</t>
+          <t>5,97; 11,37</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,43; 10,67</t>
+          <t>5,27; 10,53</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,52; 12,03</t>
+          <t>6,38; 12,03</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,41; 10,93</t>
+          <t>8,08; 11,76</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,59; 7,78</t>
+          <t>4,71; 7,87</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5,12; 8,87</t>
+          <t>5,05; 8,63</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5,4; 8,6</t>
+          <t>5,26; 8,6</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7,15; 9,84</t>
+          <t>7,34; 10,21</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>16,16%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,28; 9,27</t>
+          <t>7,31; 9,16</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,01; 12,2</t>
+          <t>9,96; 12,3</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,27; 10,32</t>
+          <t>8,3; 10,41</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8,9; 13,31</t>
+          <t>11,32; 13,65</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>13,38; 15,79</t>
+          <t>13,43; 15,85</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,6; 21,39</t>
+          <t>18,47; 21,23</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,3; 19,14</t>
+          <t>16,4; 19,18</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>15,08; 19,84</t>
+          <t>18,63; 20,65</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>10,69; 12,26</t>
+          <t>10,71; 12,25</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>14,64; 16,41</t>
+          <t>14,64; 16,47</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>12,7; 14,4</t>
+          <t>12,74; 14,46</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>13,04; 16,19</t>
+          <t>15,45; 16,96</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>141189</t>
+          <t>151153</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>318190</t>
+          <t>342116</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>459379</t>
+          <t>493269</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>138890; 183896</t>
+          <t>138381; 185138</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>200901; 257857</t>
+          <t>199203; 258709</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>133434; 177643</t>
+          <t>135882; 176485</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>123284; 161129</t>
+          <t>132507; 170399</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>277495; 341007</t>
+          <t>278852; 339370</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>437926; 512355</t>
+          <t>439956; 512141</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>313184; 379704</t>
+          <t>314942; 376906</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>296488; 341407</t>
+          <t>320542; 365084</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>430422; 510117</t>
+          <t>433116; 504669</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>658947; 749267</t>
+          <t>654472; 747803</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>466401; 541511</t>
+          <t>461554; 539548</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>434424; 488366</t>
+          <t>467956; 525811</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>219265</t>
+          <t>236349</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>279654</t>
+          <t>316148</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>498919</t>
+          <t>552497</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>67811; 103491</t>
+          <t>68083; 103333</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>102391; 144346</t>
+          <t>95934; 143376</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>108296; 155754</t>
+          <t>110270; 155832</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>159054; 260048</t>
+          <t>207191; 266490</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>124527; 170993</t>
+          <t>123785; 170097</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>172548; 227478</t>
+          <t>173943; 228936</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>200457; 259932</t>
+          <t>198750; 259741</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>209397; 323867</t>
+          <t>287821; 345485</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>201146; 258335</t>
+          <t>202826; 259458</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>285561; 352069</t>
+          <t>286200; 359360</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>323873; 399351</t>
+          <t>320958; 395617</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>404614; 565344</t>
+          <t>508786; 595904</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>49050</t>
+          <t>52614</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>60134</t>
+          <t>72098</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>109184</t>
+          <t>124712</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>14416; 34852</t>
+          <t>14849; 35033</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>18348; 42424</t>
+          <t>18934; 42691</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>17027; 39883</t>
+          <t>17625; 40088</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>37797; 65849</t>
+          <t>39813; 68786</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>28245; 52060</t>
+          <t>28453; 54158</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>24849; 48828</t>
+          <t>24137; 48201</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>35827; 66061</t>
+          <t>35060; 66054</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>48950; 72165</t>
+          <t>59407; 86422</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>47151; 79997</t>
+          <t>48397; 80896</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>48087; 83322</t>
+          <t>47403; 81040</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>59164; 94298</t>
+          <t>57669; 94282</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>93495; 128589</t>
+          <t>106152; 147654</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>409505</t>
+          <t>440116</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>657978</t>
+          <t>730361</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1067483</t>
+          <t>1170478</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>238484; 303784</t>
+          <t>239433; 300171</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>342387; 417160</t>
+          <t>340603; 420485</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>279454; 348669</t>
+          <t>280465; 351656</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>307117; 458928</t>
+          <t>398040; 479971</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>452227; 533460</t>
+          <t>453785; 535608</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>660382; 759563</t>
+          <t>655879; 753749</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>575906; 676220</t>
+          <t>579206; 677295</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>550602; 724485</t>
+          <t>694108; 769448</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>711231; 815883</t>
+          <t>712708; 815514</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1020506; 1143885</t>
+          <t>1020231; 1147576</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>877347; 994714</t>
+          <t>880258; 999194</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>926296; 1149995</t>
+          <t>1119007; 1228286</t>
         </is>
       </c>
     </row>
